--- a/shareholder-import-template.xlsx
+++ b/shareholder-import-template.xlsx
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A23"/>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -580,7 +580,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>• মোবাইল, NID ও আইডির ঘর "টেক্সট" ফরম্যাটে রাখা আছে, যাতে শুরুর শূন্য না হারায়। অন্য জায়গা থেকে কপি করলে ফরম্যাট বদলে যেতে পারে।</t>
+          <t>• মোবাইল, NID, আইডি ও চেক নম্বরের ঘর "টেক্সট" ফরম্যাটে রাখা আছে, যাতে শুরুর শূন্য না হারায়। অন্য জায়গা থেকে কপি করলে ফরম্যাট বদলে যেতে পারে।</t>
         </is>
       </c>
     </row>
@@ -601,36 +601,43 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>• ভর্তি ফি: নতুন সদস্যের ভর্তি ফি আলাদা সারিতে "ভর্তি ফি" ধরনে দিন (যেমন সঞ্চয় ১০০০ আর ভর্তি ফি ২০০ দুটি সারি)। এটি সদস্যের মূলধন, সঞ্চয় বা লভ্যাংশে ধরা হয় না, কোম্পানির আয় হিসেবে আলাদা থাকে।</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
           <t>• পরিমাণ: শুধু সংখ্যা (যেমন 1000 বা 1500.50)। কমা ও বাংলা সংখ্যাও চলে।</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>• চেক নম্বর: মাধ্যম "চেক" হলে চেক নম্বর লিখতেই হবে (ঘরটি টেক্সট ফরম্যাটে আছে, শুরুর শূন্য থাকবে)। অন্য মাধ্যমে ঘর ফাঁকা রাখুন।</t>
+          <t>• চেক নম্বর: মাধ্যম "চেক" হলে চেক নম্বর লিখতেই হবে। অন্য মাধ্যমে ঘর ফাঁকা রাখুন।</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>• যে চক্র ইতিমধ্যে ক্লোজ হয়েছে, তার তারিখের লেনদেন আমদানি হবে না। আসল ডেটা তোলার সময় কোনো চক্র ক্লোজ করার আগেই সব আমদানি করুন।</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>• যাচাইয়ে একটি সারিতেও ভুল থাকলে কিছুই সংরক্ষণ হয় না। ভুল ঠিক করে আবার দিন।</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr"/>
-    </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>নমুনার সূত্র: এই ছকের নমুনা সারির সব নাম, নম্বর ও পরিমাণ কাল্পনিক, শুধু ধরন বোঝানোর জন্য।</t>
         </is>
@@ -9645,7 +9652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3001"/>
+  <dimension ref="A1:H3000"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9845,9 +9852,36 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="n"/>
-      <c r="B6" s="7" t="n"/>
-      <c r="G6" s="7" t="n"/>
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>demo001</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>ভর্তি ফি</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>নগদ (ক্যাশ)</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="n"/>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>নমুনা: ভর্তি ফি (সদস্যের সঞ্চয়ে ধরা হয় না)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n"/>
@@ -24819,11 +24853,10 @@
       <c r="B3000" s="7" t="n"/>
       <c r="G3000" s="7" t="n"/>
     </row>
-    <row r="3001"/>
   </sheetData>
   <dataValidations count="3">
     <dataValidation sqref="C2:C3000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="ধরন" error="তালিকা থেকে বাছুন" type="list">
-      <formula1>"মাসিক সঞ্চয়,বিশেষ সঞ্চয়,মূলধন উত্তোলন,লভ্যাংশ উত্তোলন"</formula1>
+      <formula1>"মাসিক সঞ্চয়,বিশেষ সঞ্চয়,ভর্তি ফি,মূলধন উত্তোলন,লভ্যাংশ উত্তোলন"</formula1>
     </dataValidation>
     <dataValidation sqref="E2:E3000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="মাধ্যম" error="তালিকা থেকে বাছুন" type="list">
       <formula1>"নগদ (ক্যাশ),ব্যাংক ট্রান্সফার,বিকাশ/নগদ/রকেট,চেক"</formula1>
